--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,780 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133828563</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514428</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6910329</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133828566</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514435</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6910128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133828568</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514390</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6910237</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133828567</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514407</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6910132</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133828565</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>514435</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6910128</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133828562</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80466</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514416</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6910359</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133828564</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514429</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6910330</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>133828563</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133828568</v>
       </c>
       <c r="B7" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133828567</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>133828562</v>
       </c>
       <c r="B10" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>133828563</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>133828566</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133828568</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133828567</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>133828562</v>
       </c>
       <c r="B10" t="n">
-        <v>80467</v>
+        <v>80481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>133828564</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>133828563</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>133828566</v>
       </c>
       <c r="B6" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133828568</v>
       </c>
       <c r="B7" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133828567</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>133828562</v>
       </c>
       <c r="B10" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>133828564</v>
       </c>
       <c r="B11" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>133828563</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133828568</v>
       </c>
       <c r="B7" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133828567</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>133828565</v>
       </c>
       <c r="B9" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>133828562</v>
       </c>
       <c r="B10" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46417-2025 artfynd.xlsx
+++ b/artfynd/A 46417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828568</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828563</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828567</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828565</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828561</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828562</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,8 +1899,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>